--- a/sov_extract/Data/brightness_analysis_15_01.xlsx
+++ b/sov_extract/Data/brightness_analysis_15_01.xlsx
@@ -1899,7 +1899,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-01-15 14:23:54</t>
+          <t>2025-01-15 21:39:13</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -3390,7 +3390,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-01-15 14:23:54</t>
+          <t>2025-01-15 21:39:13</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -4881,7 +4881,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-01-15 14:23:54</t>
+          <t>2025-01-15 21:39:13</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6372,7 +6372,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-01-15 14:23:54</t>
+          <t>2025-01-15 21:39:13</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -7863,7 +7863,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-01-15 14:23:54</t>
+          <t>2025-01-15 21:39:13</t>
         </is>
       </c>
       <c r="B36" t="n">
